--- a/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-11.xlsx
+++ b/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Desktop\App_Uv\AppAcompanhamientoUV\Doc_Test\Pruebas_Calidad\Pruebas_Unitarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F44EBB-FDC3-42DF-B442-F3DAEAA53393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2525E45-E5CE-45BF-96BA-558D0F6CA52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2FFDA8E8-6428-4D51-9D6D-F314F8731DBF}"/>
   </bookViews>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -325,22 +325,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -364,10 +353,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -379,22 +380,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -752,49 +738,49 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="2:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -816,71 +802,71 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="2:11" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
     </row>
     <row r="10" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
@@ -910,20 +896,20 @@
       <c r="B11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="19"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -942,16 +928,16 @@
       <c r="H12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="K12" s="16"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="2:11" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="19"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="7" t="s">
         <v>16</v>
       </c>
@@ -970,12 +956,12 @@
       <c r="H13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="17"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="2:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="B14" s="19"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
@@ -994,12 +980,12 @@
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="17"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B15" s="19"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="7" t="s">
         <v>42</v>
       </c>
@@ -1018,12 +1004,12 @@
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="17"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="19"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="7" t="s">
         <v>43</v>
       </c>
@@ -1042,9 +1028,9 @@
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="17"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="14">
